--- a/data/nzd0171/nzd0171.xlsx
+++ b/data/nzd0171/nzd0171.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L686"/>
+  <dimension ref="A1:L692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29258,6 +29258,258 @@
         <v>340.36</v>
       </c>
       <c r="L686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>351.8</v>
+      </c>
+      <c r="C687" t="n">
+        <v>357.69</v>
+      </c>
+      <c r="D687" t="n">
+        <v>357.18</v>
+      </c>
+      <c r="E687" t="n">
+        <v>359.53</v>
+      </c>
+      <c r="F687" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="G687" t="n">
+        <v>353.32</v>
+      </c>
+      <c r="H687" t="n">
+        <v>355.5</v>
+      </c>
+      <c r="I687" t="n">
+        <v>363.19</v>
+      </c>
+      <c r="J687" t="n">
+        <v>347.72</v>
+      </c>
+      <c r="K687" t="n">
+        <v>340.62</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>351.44</v>
+      </c>
+      <c r="C688" t="n">
+        <v>356.98</v>
+      </c>
+      <c r="D688" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="E688" t="n">
+        <v>358.65</v>
+      </c>
+      <c r="F688" t="n">
+        <v>355.85</v>
+      </c>
+      <c r="G688" t="n">
+        <v>353.05</v>
+      </c>
+      <c r="H688" t="n">
+        <v>355.31</v>
+      </c>
+      <c r="I688" t="n">
+        <v>363.08</v>
+      </c>
+      <c r="J688" t="n">
+        <v>347.69</v>
+      </c>
+      <c r="K688" t="n">
+        <v>340.25</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>351.06</v>
+      </c>
+      <c r="C689" t="n">
+        <v>357.21</v>
+      </c>
+      <c r="D689" t="n">
+        <v>356.91</v>
+      </c>
+      <c r="E689" t="n">
+        <v>358.94</v>
+      </c>
+      <c r="F689" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="G689" t="n">
+        <v>353.04</v>
+      </c>
+      <c r="H689" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="I689" t="n">
+        <v>363.05</v>
+      </c>
+      <c r="J689" t="n">
+        <v>347.51</v>
+      </c>
+      <c r="K689" t="n">
+        <v>340.14</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>351.87</v>
+      </c>
+      <c r="C690" t="n">
+        <v>358.08</v>
+      </c>
+      <c r="D690" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="E690" t="n">
+        <v>359.57</v>
+      </c>
+      <c r="F690" t="n">
+        <v>357.3</v>
+      </c>
+      <c r="G690" t="n">
+        <v>353.2</v>
+      </c>
+      <c r="H690" t="n">
+        <v>355.36</v>
+      </c>
+      <c r="I690" t="n">
+        <v>363.19</v>
+      </c>
+      <c r="J690" t="n">
+        <v>347.7</v>
+      </c>
+      <c r="K690" t="n">
+        <v>340.07</v>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="C691" t="n">
+        <v>358.38</v>
+      </c>
+      <c r="D691" t="n">
+        <v>357.01</v>
+      </c>
+      <c r="E691" t="n">
+        <v>358.82</v>
+      </c>
+      <c r="F691" t="n">
+        <v>356.5</v>
+      </c>
+      <c r="G691" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="H691" t="n">
+        <v>355.11</v>
+      </c>
+      <c r="I691" t="n">
+        <v>363.21</v>
+      </c>
+      <c r="J691" t="n">
+        <v>347.64</v>
+      </c>
+      <c r="K691" t="n">
+        <v>340.22</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>352.22</v>
+      </c>
+      <c r="C692" t="n">
+        <v>358.21</v>
+      </c>
+      <c r="D692" t="n">
+        <v>356.76</v>
+      </c>
+      <c r="E692" t="n">
+        <v>358.49</v>
+      </c>
+      <c r="F692" t="n">
+        <v>356.17</v>
+      </c>
+      <c r="G692" t="n">
+        <v>352.83</v>
+      </c>
+      <c r="H692" t="n">
+        <v>355.21</v>
+      </c>
+      <c r="I692" t="n">
+        <v>363.55</v>
+      </c>
+      <c r="J692" t="n">
+        <v>347.71</v>
+      </c>
+      <c r="K692" t="n">
+        <v>340.35</v>
+      </c>
+      <c r="L692" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29274,7 +29526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B764"/>
+  <dimension ref="A1:B770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36917,6 +37169,66 @@
       </c>
       <c r="B764" t="n">
         <v>-0.9</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -37085,28 +37397,28 @@
         <v>0.0462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1456361369484181</v>
+        <v>-0.146222862422604</v>
       </c>
       <c r="J2" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K2" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1058459872707475</v>
+        <v>0.1082342536915074</v>
       </c>
       <c r="M2" t="n">
-        <v>2.379842778414311</v>
+        <v>2.362380234133559</v>
       </c>
       <c r="N2" t="n">
-        <v>8.813512854888</v>
+        <v>8.739431498514854</v>
       </c>
       <c r="O2" t="n">
-        <v>2.968756112395897</v>
+        <v>2.956252949007384</v>
       </c>
       <c r="P2" t="n">
-        <v>356.0095922230938</v>
+        <v>356.0165877565415</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37163,28 +37475,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1436469801061207</v>
+        <v>-0.1402636112139005</v>
       </c>
       <c r="J3" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K3" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1299081919376767</v>
+        <v>0.1259343164687595</v>
       </c>
       <c r="M3" t="n">
-        <v>1.902571611473088</v>
+        <v>1.902198939993006</v>
       </c>
       <c r="N3" t="n">
-        <v>6.798206482101929</v>
+        <v>6.774177513442674</v>
       </c>
       <c r="O3" t="n">
-        <v>2.607337048043833</v>
+        <v>2.602725016870333</v>
       </c>
       <c r="P3" t="n">
-        <v>359.6455880638115</v>
+        <v>359.605207928765</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37241,28 +37553,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1413886134809228</v>
+        <v>-0.1385654099583327</v>
       </c>
       <c r="J4" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K4" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09513773655020796</v>
+        <v>0.09294741021023112</v>
       </c>
       <c r="M4" t="n">
-        <v>2.211255865499713</v>
+        <v>2.205490733642972</v>
       </c>
       <c r="N4" t="n">
-        <v>9.352578077354503</v>
+        <v>9.295470917332912</v>
       </c>
       <c r="O4" t="n">
-        <v>3.058198501954133</v>
+        <v>3.048847473609153</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1635468749001</v>
+        <v>359.1298592963815</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37319,28 +37631,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.152803943672479</v>
+        <v>-0.1493220278074734</v>
       </c>
       <c r="J5" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K5" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1293364722821017</v>
+        <v>0.1256025663688457</v>
       </c>
       <c r="M5" t="n">
-        <v>2.132461346703898</v>
+        <v>2.130513421921643</v>
       </c>
       <c r="N5" t="n">
-        <v>7.731633804503764</v>
+        <v>7.700602030967185</v>
       </c>
       <c r="O5" t="n">
-        <v>2.780581558685838</v>
+        <v>2.774995861432443</v>
       </c>
       <c r="P5" t="n">
-        <v>361.0723493267264</v>
+        <v>361.0308058582499</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37397,28 +37709,28 @@
         <v>0.0562</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1188789107423945</v>
+        <v>-0.1172028368307767</v>
       </c>
       <c r="J6" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K6" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06532311962489412</v>
+        <v>0.06458459087956503</v>
       </c>
       <c r="M6" t="n">
-        <v>2.454773012859995</v>
+        <v>2.441248407674634</v>
       </c>
       <c r="N6" t="n">
-        <v>9.946654361588614</v>
+        <v>9.870028679773874</v>
       </c>
       <c r="O6" t="n">
-        <v>3.153831695190568</v>
+        <v>3.141660178913988</v>
       </c>
       <c r="P6" t="n">
-        <v>358.6924892779955</v>
+        <v>358.6724892737589</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37475,28 +37787,28 @@
         <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09694539739436168</v>
+        <v>-0.09970926665349145</v>
       </c>
       <c r="J7" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K7" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05105742868812901</v>
+        <v>0.05460225031846211</v>
       </c>
       <c r="M7" t="n">
-        <v>2.26468472384834</v>
+        <v>2.262086988550629</v>
       </c>
       <c r="N7" t="n">
-        <v>8.592275440538538</v>
+        <v>8.539680591251251</v>
       </c>
       <c r="O7" t="n">
-        <v>2.931258337393437</v>
+        <v>2.922273189017627</v>
       </c>
       <c r="P7" t="n">
-        <v>357.2754340465695</v>
+        <v>357.3084166121385</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37553,28 +37865,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001667494564164045</v>
+        <v>-0.0005505411067294977</v>
       </c>
       <c r="J8" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K8" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L8" t="n">
-        <v>1.607280785798082e-05</v>
+        <v>1.779509585575489e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.229813503589566</v>
+        <v>2.223175863202696</v>
       </c>
       <c r="N8" t="n">
-        <v>8.509478192849361</v>
+        <v>8.449771386373152</v>
       </c>
       <c r="O8" t="n">
-        <v>2.917100991198172</v>
+        <v>2.906849047744508</v>
       </c>
       <c r="P8" t="n">
-        <v>356.5247729285757</v>
+        <v>356.5512415775781</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37631,28 +37943,28 @@
         <v>0.106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07089730340429479</v>
+        <v>0.06934288381421008</v>
       </c>
       <c r="J9" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K9" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0213065333892104</v>
+        <v>0.02073560856132928</v>
       </c>
       <c r="M9" t="n">
-        <v>2.556966150271237</v>
+        <v>2.542192445770336</v>
       </c>
       <c r="N9" t="n">
-        <v>11.3570656826087</v>
+        <v>11.26557946347561</v>
       </c>
       <c r="O9" t="n">
-        <v>3.370024581899767</v>
+        <v>3.356423612042379</v>
       </c>
       <c r="P9" t="n">
-        <v>362.2138490211719</v>
+        <v>362.232394491675</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37709,28 +38021,28 @@
         <v>0.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1125401617437438</v>
+        <v>0.1112045092631784</v>
       </c>
       <c r="J10" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K10" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04462446368617035</v>
+        <v>0.04432525375003005</v>
       </c>
       <c r="M10" t="n">
-        <v>2.759417175556666</v>
+        <v>2.74110790432466</v>
       </c>
       <c r="N10" t="n">
-        <v>13.3379469600524</v>
+        <v>13.22727051726641</v>
       </c>
       <c r="O10" t="n">
-        <v>3.652115408917467</v>
+        <v>3.636931469971136</v>
       </c>
       <c r="P10" t="n">
-        <v>345.4230807488603</v>
+        <v>345.4390185062105</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37787,28 +38099,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1374934368703698</v>
+        <v>0.1332331081938014</v>
       </c>
       <c r="J11" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K11" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0583046979472025</v>
+        <v>0.05566035506207523</v>
       </c>
       <c r="M11" t="n">
-        <v>2.952830894524966</v>
+        <v>2.94501783831503</v>
       </c>
       <c r="N11" t="n">
-        <v>15.01908929352289</v>
+        <v>14.94077514290674</v>
       </c>
       <c r="O11" t="n">
-        <v>3.875446979836376</v>
+        <v>3.865329887979387</v>
       </c>
       <c r="P11" t="n">
-        <v>339.0611665012805</v>
+        <v>339.1120038744248</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37846,7 +38158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L686"/>
+  <dimension ref="A1:L692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80381,6 +80693,378 @@
         </is>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-36.77813890115726,175.0093083923917</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-36.77886102425238,175.009373713347</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-36.779540752314716,175.009622935682</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-36.78018127868782,175.0100390456473</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-36.78077366584877,175.01054091469337</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-36.781327498060065,175.01111939208707</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>-36.78184771769251,175.01174039729446</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>-36.78232198284462,175.01240812177664</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>-36.78275777143834,175.01313849033048</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>-36.78312765207923,175.0139144896884</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-36.778138945551454,175.00930436002665</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-36.77886203382966,175.0093658594532</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-36.77954316312737,175.00961556833028</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-36.780185461729815,175.01003067070693</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-36.78077714308238,175.01053576769945</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-36.78132915414419,175.01111717623652</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>-36.781848891703945,175.01173884800704</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>-36.78232278868467,175.01240740420593</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>-36.782758016574626,175.01313834864155</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>-36.783130675433085,175.01391274220356</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>-36.77813899241183,175.00930010364132</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>-36.77886170678355,175.00936840367234</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-36.77954166910269,175.0096201340131</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-36.78018408322741,175.01003343063056</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>-36.78077273858646,175.01054228722498</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>-36.78132921548064,175.011117094168</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>-36.781849571394766,175.01173795105117</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>-36.78232300845924,175.01240720850484</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>-36.782759487392305,175.01313749850786</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>-36.78313157426801,175.013912222681</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>-36.77813889252504,175.00930917646266</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>-36.77886046969562,175.00937802745761</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-36.77953881687326,175.00962885031615</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-36.78018108854953,175.0100394263264</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>-36.78076873976751,175.0105482062673</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>-36.78132823409745,175.0111184072646</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>-36.78184858275357,175.01173925571428</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>-36.78232198284462,175.01240812177664</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>-36.782757934862516,175.01313839587118</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>-36.78313214625387,175.01391189207573</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>-36.77813885183022,175.00931287279727</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>-36.7788600431134,175.00938134600418</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-36.77954132955159,175.00962117166827</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>-36.78018465364221,175.0100322885932</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>-36.7807733760793,175.0105413436095</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>-36.781329522162864,175.01111668382526</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>-36.78185012750542,175.01173721717814</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>-36.782321836328244,175.0124082522441</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>-36.782758425135086,175.0131381124933</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>-36.78313092056989,175.01391260051557</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>-36.77813884936388,175.00931309681755</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>-36.77886028484334,175.00937946549448</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>-36.7795421784293,175.00961857753032</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>-36.78018622228286,175.0100291479904</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>-36.78077528855781,175.0105385127629</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>-36.78133050354603,175.01111537072856</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>-36.78184950960469,175.0117380325926</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>-36.782319345549894,175.01241047018982</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>-36.78275785315042,175.01313844310081</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>-36.78312985831043,175.01391321449677</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0171/nzd0171.xlsx
+++ b/data/nzd0171/nzd0171.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L692"/>
+  <dimension ref="A1:L695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29510,6 +29510,132 @@
         <v>340.35</v>
       </c>
       <c r="L692" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="C693" t="n">
+        <v>358.45</v>
+      </c>
+      <c r="D693" t="n">
+        <v>356.74</v>
+      </c>
+      <c r="E693" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="F693" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="G693" t="n">
+        <v>353.09</v>
+      </c>
+      <c r="H693" t="n">
+        <v>355.59</v>
+      </c>
+      <c r="I693" t="n">
+        <v>363.89</v>
+      </c>
+      <c r="J693" t="n">
+        <v>348.01</v>
+      </c>
+      <c r="K693" t="n">
+        <v>340.76</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>352.53</v>
+      </c>
+      <c r="C694" t="n">
+        <v>358.46</v>
+      </c>
+      <c r="D694" t="n">
+        <v>356.59</v>
+      </c>
+      <c r="E694" t="n">
+        <v>358.39</v>
+      </c>
+      <c r="F694" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="G694" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="H694" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="I694" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="J694" t="n">
+        <v>348.11</v>
+      </c>
+      <c r="K694" t="n">
+        <v>340.68</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="C695" t="n">
+        <v>358.65</v>
+      </c>
+      <c r="D695" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="E695" t="n">
+        <v>358.26</v>
+      </c>
+      <c r="F695" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="G695" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="H695" t="n">
+        <v>355.59</v>
+      </c>
+      <c r="I695" t="n">
+        <v>363.87</v>
+      </c>
+      <c r="J695" t="n">
+        <v>348.01</v>
+      </c>
+      <c r="K695" t="n">
+        <v>340.83</v>
+      </c>
+      <c r="L695" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29526,7 +29652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B770"/>
+  <dimension ref="A1:B773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37229,6 +37355,36 @@
       </c>
       <c r="B770" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -37397,28 +37553,28 @@
         <v>0.0462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.146222862422604</v>
+        <v>-0.1456906077468232</v>
       </c>
       <c r="J2" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K2" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1082342536915074</v>
+        <v>0.1083351023340812</v>
       </c>
       <c r="M2" t="n">
-        <v>2.362380234133559</v>
+        <v>2.355156606842144</v>
       </c>
       <c r="N2" t="n">
-        <v>8.739431498514854</v>
+        <v>8.703369262449046</v>
       </c>
       <c r="O2" t="n">
-        <v>2.956252949007384</v>
+        <v>2.950147328939531</v>
       </c>
       <c r="P2" t="n">
-        <v>356.0165877565415</v>
+        <v>356.0102140456731</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37475,28 +37631,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1402636112139005</v>
+        <v>-0.1379628484102695</v>
       </c>
       <c r="J3" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K3" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1259343164687595</v>
+        <v>0.1227658586026671</v>
       </c>
       <c r="M3" t="n">
-        <v>1.902198939993006</v>
+        <v>1.90492560973502</v>
       </c>
       <c r="N3" t="n">
-        <v>6.774177513442674</v>
+        <v>6.775698187404783</v>
       </c>
       <c r="O3" t="n">
-        <v>2.602725016870333</v>
+        <v>2.603017131600325</v>
       </c>
       <c r="P3" t="n">
-        <v>359.605207928765</v>
+        <v>359.5776561845342</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37553,28 +37709,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1385654099583327</v>
+        <v>-0.137497726953446</v>
       </c>
       <c r="J4" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K4" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09294741021023112</v>
+        <v>0.09230421183456361</v>
       </c>
       <c r="M4" t="n">
-        <v>2.205490733642972</v>
+        <v>2.201058210590114</v>
       </c>
       <c r="N4" t="n">
-        <v>9.295470917332912</v>
+        <v>9.261933686656436</v>
       </c>
       <c r="O4" t="n">
-        <v>3.048847473609153</v>
+        <v>3.04334251878694</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1298592963815</v>
+        <v>359.1170744140246</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37631,28 +37787,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1493220278074734</v>
+        <v>-0.1481428971000077</v>
       </c>
       <c r="J5" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K5" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1256025663688457</v>
+        <v>0.1246850540309905</v>
       </c>
       <c r="M5" t="n">
-        <v>2.130513421921643</v>
+        <v>2.126898617960768</v>
       </c>
       <c r="N5" t="n">
-        <v>7.700602030967185</v>
+        <v>7.675442829605717</v>
       </c>
       <c r="O5" t="n">
-        <v>2.774995861432443</v>
+        <v>2.770458956491815</v>
       </c>
       <c r="P5" t="n">
-        <v>361.0308058582499</v>
+        <v>361.0166867980622</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37709,28 +37865,28 @@
         <v>0.0562</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1172028368307767</v>
+        <v>-0.1166235932155971</v>
       </c>
       <c r="J6" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K6" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06458459087956503</v>
+        <v>0.06448949070245968</v>
       </c>
       <c r="M6" t="n">
-        <v>2.441248407674634</v>
+        <v>2.433385344811008</v>
       </c>
       <c r="N6" t="n">
-        <v>9.870028679773874</v>
+        <v>9.829340673916318</v>
       </c>
       <c r="O6" t="n">
-        <v>3.141660178913988</v>
+        <v>3.135177933374168</v>
       </c>
       <c r="P6" t="n">
-        <v>358.6724892737589</v>
+        <v>358.6655535340572</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37787,28 +37943,28 @@
         <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09970926665349145</v>
+        <v>-0.1010212685653077</v>
       </c>
       <c r="J7" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K7" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05460225031846211</v>
+        <v>0.05635778372756883</v>
       </c>
       <c r="M7" t="n">
-        <v>2.262086988550629</v>
+        <v>2.260327504141764</v>
       </c>
       <c r="N7" t="n">
-        <v>8.539680591251251</v>
+        <v>8.512770385796903</v>
       </c>
       <c r="O7" t="n">
-        <v>2.922273189017627</v>
+        <v>2.917665228534093</v>
       </c>
       <c r="P7" t="n">
-        <v>357.3084166121385</v>
+        <v>357.3241275066329</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37865,28 +38021,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0005505411067294977</v>
+        <v>-0.001390889762564307</v>
       </c>
       <c r="J8" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K8" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L8" t="n">
-        <v>1.779509585575489e-06</v>
+        <v>1.144976254341401e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.223175863202696</v>
+        <v>2.218327628821305</v>
       </c>
       <c r="N8" t="n">
-        <v>8.449771386373152</v>
+        <v>8.417357959571158</v>
       </c>
       <c r="O8" t="n">
-        <v>2.906849047744508</v>
+        <v>2.90126833636104</v>
       </c>
       <c r="P8" t="n">
-        <v>356.5512415775781</v>
+        <v>356.5613045353321</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37943,28 +38099,28 @@
         <v>0.106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06934288381421008</v>
+        <v>0.06914818942785435</v>
       </c>
       <c r="J9" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K9" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02073560856132928</v>
+        <v>0.02079441223182388</v>
       </c>
       <c r="M9" t="n">
-        <v>2.542192445770336</v>
+        <v>2.532130393606143</v>
       </c>
       <c r="N9" t="n">
-        <v>11.26557946347561</v>
+        <v>11.21710248559874</v>
       </c>
       <c r="O9" t="n">
-        <v>3.356423612042379</v>
+        <v>3.349194303948152</v>
       </c>
       <c r="P9" t="n">
-        <v>362.232394491675</v>
+        <v>362.234725966925</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38021,28 +38177,28 @@
         <v>0.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1112045092631784</v>
+        <v>0.1108717350714039</v>
       </c>
       <c r="J10" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K10" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04432525375003005</v>
+        <v>0.0444309133866978</v>
       </c>
       <c r="M10" t="n">
-        <v>2.74110790432466</v>
+        <v>2.730647311787472</v>
       </c>
       <c r="N10" t="n">
-        <v>13.22727051726641</v>
+        <v>13.170745750093</v>
       </c>
       <c r="O10" t="n">
-        <v>3.636931469971136</v>
+        <v>3.629152208173832</v>
       </c>
       <c r="P10" t="n">
-        <v>345.4390185062105</v>
+        <v>345.4430034178963</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38099,28 +38255,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1332331081938014</v>
+        <v>0.1315717912338316</v>
       </c>
       <c r="J11" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K11" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05566035506207523</v>
+        <v>0.05474042824086067</v>
       </c>
       <c r="M11" t="n">
-        <v>2.94501783831503</v>
+        <v>2.939141443306203</v>
       </c>
       <c r="N11" t="n">
-        <v>14.94077514290674</v>
+        <v>14.89224922313789</v>
       </c>
       <c r="O11" t="n">
-        <v>3.865329887979387</v>
+        <v>3.85904770936275</v>
       </c>
       <c r="P11" t="n">
-        <v>339.1120038744248</v>
+        <v>339.1318975379366</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38158,7 +38314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L692"/>
+  <dimension ref="A1:L695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81065,6 +81221,192 @@
         </is>
       </c>
     </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>-36.778138779072535,175.00931948139547</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>-36.77885994357754,175.0093821203317</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>-36.7795422463395,175.0096183699993</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>-36.78018607967916,175.01002943349974</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>-36.78077453515719,175.01053962794492</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>-36.781328908798386,175.01111750451068</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>-36.781847161581815,175.01174113116738</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>-36.7823168547715,175.0124126881354</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>-36.78275540178759,175.01313985999022</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>-36.78312650810749,175.0139151508989</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>-36.778138811135285,175.00931656913187</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>-36.77885992935813,175.00938223094994</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>-36.77954275566609,175.00961681351652</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>-36.78018669762849,175.01002819629252</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>-36.78077523060392,175.01053859854616</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>-36.78132884746194,175.01111758657922</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>-36.781847779482575,175.011740315753</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>-36.78231714780426,175.01241242720064</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>-36.78275458466664,175.01314033228664</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>-36.78312716180563,175.01391477306433</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>-36.778138777839345,175.0093195934056</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>-36.77885965918932,175.00938433269604</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>-36.779542687755885,175.00961702104755</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>-36.780187315577805,175.01002695908534</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>-36.78077563628118,175.0105379980635</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>-36.78132884746194,175.01111758657922</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>-36.781847161581815,175.01174113116738</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>-36.78231700128788,175.01241255766806</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>-36.78275540178759,175.01313985999022</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>-36.78312593612163,175.0139154815041</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0171/nzd0171.xlsx
+++ b/data/nzd0171/nzd0171.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L695"/>
+  <dimension ref="A1:L696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29636,6 +29636,48 @@
         <v>340.83</v>
       </c>
       <c r="L695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>353.35</v>
+      </c>
+      <c r="C696" t="n">
+        <v>358.67</v>
+      </c>
+      <c r="D696" t="n">
+        <v>356.6</v>
+      </c>
+      <c r="E696" t="n">
+        <v>358.59</v>
+      </c>
+      <c r="F696" t="n">
+        <v>356.12</v>
+      </c>
+      <c r="G696" t="n">
+        <v>353.67</v>
+      </c>
+      <c r="H696" t="n">
+        <v>355.63</v>
+      </c>
+      <c r="I696" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="J696" t="n">
+        <v>347.75</v>
+      </c>
+      <c r="K696" t="n">
+        <v>340.56</v>
+      </c>
+      <c r="L696" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29652,7 +29694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B773"/>
+  <dimension ref="A1:B775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37385,6 +37427,26 @@
       </c>
       <c r="B773" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B774" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B775" t="n">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>
@@ -37553,28 +37615,28 @@
         <v>0.0462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1456906077468232</v>
+        <v>-0.1453248662471745</v>
       </c>
       <c r="J2" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K2" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1083351023340812</v>
+        <v>0.1081004832025803</v>
       </c>
       <c r="M2" t="n">
-        <v>2.355156606842144</v>
+        <v>2.353801835226292</v>
       </c>
       <c r="N2" t="n">
-        <v>8.703369262449046</v>
+        <v>8.693173485109783</v>
       </c>
       <c r="O2" t="n">
-        <v>2.950147328939531</v>
+        <v>2.948418811008671</v>
       </c>
       <c r="P2" t="n">
-        <v>356.0102140456731</v>
+        <v>356.0058178161696</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37631,28 +37693,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1379628484102695</v>
+        <v>-0.1371563322008012</v>
       </c>
       <c r="J3" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K3" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1227658586026671</v>
+        <v>0.1216359657113191</v>
       </c>
       <c r="M3" t="n">
-        <v>1.90492560973502</v>
+        <v>1.906043011045524</v>
       </c>
       <c r="N3" t="n">
-        <v>6.775698187404783</v>
+        <v>6.777264763513547</v>
       </c>
       <c r="O3" t="n">
-        <v>2.603017131600325</v>
+        <v>2.603318029652456</v>
       </c>
       <c r="P3" t="n">
-        <v>359.5776561845342</v>
+        <v>359.5679618229194</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37709,28 +37771,28 @@
         <v>0.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.137497726953446</v>
+        <v>-0.1371554521093781</v>
       </c>
       <c r="J4" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K4" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09230421183456361</v>
+        <v>0.09210822240784111</v>
       </c>
       <c r="M4" t="n">
-        <v>2.201058210590114</v>
+        <v>2.199510350243931</v>
       </c>
       <c r="N4" t="n">
-        <v>9.261933686656436</v>
+        <v>9.250645182885549</v>
       </c>
       <c r="O4" t="n">
-        <v>3.04334251878694</v>
+        <v>3.041487330712648</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1170744140246</v>
+        <v>359.1129602547912</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37787,28 +37849,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1481428971000077</v>
+        <v>-0.1476922567184445</v>
       </c>
       <c r="J5" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K5" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1246850540309905</v>
+        <v>0.1242828627482333</v>
       </c>
       <c r="M5" t="n">
-        <v>2.126898617960768</v>
+        <v>2.125953629435046</v>
       </c>
       <c r="N5" t="n">
-        <v>7.675442829605717</v>
+        <v>7.667931823205327</v>
       </c>
       <c r="O5" t="n">
-        <v>2.770458956491815</v>
+        <v>2.769103071972101</v>
       </c>
       <c r="P5" t="n">
-        <v>361.0166867980622</v>
+        <v>361.0112700801267</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37865,28 +37927,28 @@
         <v>0.0562</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1166235932155971</v>
+        <v>-0.1164508418419275</v>
       </c>
       <c r="J6" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K6" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06448949070245968</v>
+        <v>0.06448020528824217</v>
       </c>
       <c r="M6" t="n">
-        <v>2.433385344811008</v>
+        <v>2.430679001233822</v>
       </c>
       <c r="N6" t="n">
-        <v>9.829340673916318</v>
+        <v>9.815716897900169</v>
       </c>
       <c r="O6" t="n">
-        <v>3.135177933374168</v>
+        <v>3.133004452263062</v>
       </c>
       <c r="P6" t="n">
-        <v>358.6655535340572</v>
+        <v>358.6634770546682</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37943,28 +38005,28 @@
         <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1010212685653077</v>
+        <v>-0.101286414154445</v>
       </c>
       <c r="J7" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K7" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05635778372756883</v>
+        <v>0.0567827290778179</v>
       </c>
       <c r="M7" t="n">
-        <v>2.260327504141764</v>
+        <v>2.258681856562562</v>
       </c>
       <c r="N7" t="n">
-        <v>8.512770385796903</v>
+        <v>8.501744797378182</v>
       </c>
       <c r="O7" t="n">
-        <v>2.917665228534093</v>
+        <v>2.915775162350174</v>
       </c>
       <c r="P7" t="n">
-        <v>357.3241275066329</v>
+        <v>357.3273145687048</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38021,28 +38083,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001390889762564307</v>
+        <v>-0.001647984156571181</v>
       </c>
       <c r="J8" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K8" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L8" t="n">
-        <v>1.144976254341401e-05</v>
+        <v>1.61175632491517e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.218327628821305</v>
+        <v>2.21657791113919</v>
       </c>
       <c r="N8" t="n">
-        <v>8.417357959571158</v>
+        <v>8.406396509510977</v>
       </c>
       <c r="O8" t="n">
-        <v>2.90126833636104</v>
+        <v>2.899378641969858</v>
       </c>
       <c r="P8" t="n">
-        <v>356.5613045353321</v>
+        <v>356.5643948216715</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38099,28 +38161,28 @@
         <v>0.106</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06914818942785435</v>
+        <v>0.06911674103377624</v>
       </c>
       <c r="J9" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K9" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02079441223182388</v>
+        <v>0.02083420377912271</v>
       </c>
       <c r="M9" t="n">
-        <v>2.532130393606143</v>
+        <v>2.528635196457953</v>
       </c>
       <c r="N9" t="n">
-        <v>11.21710248559874</v>
+        <v>11.2009799748177</v>
       </c>
       <c r="O9" t="n">
-        <v>3.349194303948152</v>
+        <v>3.346786514676086</v>
       </c>
       <c r="P9" t="n">
-        <v>362.234725966925</v>
+        <v>362.2351039780559</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38177,28 +38239,28 @@
         <v>0.1949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1108717350714039</v>
+        <v>0.110674007830741</v>
       </c>
       <c r="J10" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K10" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0444309133866978</v>
+        <v>0.04439874410038946</v>
       </c>
       <c r="M10" t="n">
-        <v>2.730647311787472</v>
+        <v>2.727533783789259</v>
       </c>
       <c r="N10" t="n">
-        <v>13.170745750093</v>
+        <v>13.15247516593216</v>
       </c>
       <c r="O10" t="n">
-        <v>3.629152208173832</v>
+        <v>3.626634137314125</v>
       </c>
       <c r="P10" t="n">
-        <v>345.4430034178963</v>
+        <v>345.4453801083454</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38255,28 +38317,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1315717912338316</v>
+        <v>0.1309635097819083</v>
       </c>
       <c r="J11" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K11" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05474042824086067</v>
+        <v>0.0543877375126014</v>
       </c>
       <c r="M11" t="n">
-        <v>2.939141443306203</v>
+        <v>2.937391858712575</v>
       </c>
       <c r="N11" t="n">
-        <v>14.89224922313789</v>
+        <v>14.87725828949717</v>
       </c>
       <c r="O11" t="n">
-        <v>3.85904770936275</v>
+        <v>3.857104910356623</v>
       </c>
       <c r="P11" t="n">
-        <v>339.1318975379366</v>
+        <v>339.1392091087262</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38314,7 +38376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L695"/>
+  <dimension ref="A1:L696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81407,6 +81469,68 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>-36.77813871001407,175.00932575396322</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>-36.7788596307505,175.00938455393248</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>-36.77954272171099,175.00961691728205</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>-36.7801857469372,175.01003009968824</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>-36.78077557832729,175.01053808384677</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>-36.78132535128428,175.0111222644858</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>-36.781846914421514,175.01174145733316</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>-36.78231612218961,175.01241334047236</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>-36.78275752630205,175.0131386320194</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>-36.783128142352844,175.01391420631248</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
